--- a/data/base/Backlog_8.xlsx
+++ b/data/base/Backlog_8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CE819D-70D0-4349-B2C6-152CD808899E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18DD01EB-BB6E-4617-93A6-6AA4CA74C7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="33">
   <si>
     <t>Status</t>
   </si>
@@ -137,13 +137,16 @@
   </si>
   <si>
     <t>Mara Neves</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,12 +191,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
       <family val="2"/>
@@ -255,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -296,7 +293,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -848,7 +844,7 @@
         <v>46083</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -893,7 +889,7 @@
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="7">
@@ -918,7 +914,7 @@
         <v>46083</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>27</v>
@@ -969,7 +965,7 @@
       <c r="K12" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K16" s="19"/>
+      <c r="K16" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
@@ -1064,7 +1060,7 @@
         <v>46083</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>7</v>
@@ -1099,7 +1095,7 @@
         <v>46083</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>7</v>
@@ -1169,7 +1165,7 @@
         <v>46083</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>7</v>
@@ -1204,7 +1200,7 @@
         <v>46083</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>7</v>
@@ -1239,7 +1235,7 @@
         <v>46083</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>7</v>
@@ -1274,7 +1270,7 @@
         <v>46083</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>7</v>
@@ -1309,7 +1305,7 @@
         <v>46083</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>7</v>
@@ -1344,7 +1340,7 @@
         <v>46083</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>7</v>
@@ -1379,7 +1375,7 @@
         <v>46083</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>7</v>
@@ -1449,7 +1445,7 @@
         <v>46083</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>7</v>
@@ -1484,7 +1480,7 @@
         <v>46083</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>7</v>
@@ -1589,7 +1585,7 @@
         <v>46083</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>7</v>
@@ -1624,7 +1620,7 @@
         <v>46083</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>7</v>
@@ -1694,7 +1690,7 @@
         <v>46083</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>7</v>
@@ -1729,7 +1725,7 @@
         <v>46083</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>7</v>
@@ -1834,7 +1830,7 @@
         <v>46083</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>7</v>
@@ -1869,7 +1865,7 @@
         <v>46083</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>7</v>
@@ -1966,5 +1962,6 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>